--- a/temp/alpha_sweep_results.xlsx
+++ b/temp/alpha_sweep_results.xlsx
@@ -438,34 +438,34 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="K2">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="L2">
-        <v>28.8</v>
+        <v>30.3</v>
       </c>
       <c r="M2">
-        <v>30.8</v>
+        <v>32.5</v>
       </c>
       <c r="N2">
-        <v>37.8</v>
+        <v>41.5</v>
       </c>
       <c r="O2">
-        <v>55.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="P2">
-        <v>95.39999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -473,49 +473,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="C3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="D3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="E3">
-        <v>25.9</v>
+        <v>30.5</v>
       </c>
       <c r="F3">
-        <v>25.9</v>
+        <v>30.6</v>
       </c>
       <c r="G3">
-        <v>25.9</v>
+        <v>30.8</v>
       </c>
       <c r="H3">
-        <v>26.1</v>
+        <v>31.1</v>
       </c>
       <c r="I3">
-        <v>26.3</v>
+        <v>31.5</v>
       </c>
       <c r="J3">
-        <v>27.1</v>
+        <v>32.2</v>
       </c>
       <c r="K3">
-        <v>28.5</v>
+        <v>34.1</v>
       </c>
       <c r="L3">
-        <v>30.8</v>
+        <v>35.9</v>
       </c>
       <c r="M3">
-        <v>31.6</v>
+        <v>37.4</v>
       </c>
       <c r="N3">
-        <v>39.5</v>
+        <v>45.7</v>
       </c>
       <c r="O3">
-        <v>57.2</v>
+        <v>61.6</v>
       </c>
       <c r="P3">
-        <v>87.3</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -523,49 +523,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -573,49 +573,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>25.3</v>
       </c>
       <c r="F5">
+        <v>25.4</v>
+      </c>
+      <c r="G5">
         <v>25.5</v>
       </c>
-      <c r="G5">
-        <v>25.7</v>
-      </c>
       <c r="H5">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="I5">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="J5">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="K5">
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="L5">
-        <v>31.1</v>
+        <v>32.1</v>
       </c>
       <c r="M5">
-        <v>32.4</v>
+        <v>34.2</v>
       </c>
       <c r="N5">
-        <v>40.9</v>
+        <v>42.7</v>
       </c>
       <c r="O5">
-        <v>57.59999999999999</v>
+        <v>69.19999999999999</v>
       </c>
       <c r="P5">
-        <v>95.5</v>
+        <v>98.5</v>
       </c>
     </row>
   </sheetData>
@@ -698,49 +698,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="C2">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="D2">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="E2">
-        <v>51.3</v>
+        <v>52.2</v>
       </c>
       <c r="F2">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="G2">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="H2">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="I2">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="J2">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="K2">
+        <v>50.8</v>
+      </c>
+      <c r="L2">
         <v>50.6</v>
-      </c>
-      <c r="L2">
-        <v>50.4</v>
       </c>
       <c r="M2">
         <v>50.4</v>
       </c>
       <c r="N2">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="O2">
-        <v>46.2</v>
+        <v>43.5</v>
       </c>
       <c r="P2">
-        <v>36</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -748,49 +748,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J3">
-        <v>97.89999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K3">
-        <v>97.89999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="L3">
-        <v>97.89999999999999</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="M3">
-        <v>97.89999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="N3">
-        <v>97.89999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="O3">
-        <v>97.39999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="P3">
-        <v>96.5</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -848,49 +848,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="C5">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="D5">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="E5">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="F5">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="G5">
-        <v>50.4</v>
+        <v>48.4</v>
       </c>
       <c r="H5">
-        <v>50.3</v>
+        <v>48.2</v>
       </c>
       <c r="I5">
-        <v>50.2</v>
+        <v>48.2</v>
       </c>
       <c r="J5">
-        <v>50.1</v>
+        <v>47.9</v>
       </c>
       <c r="K5">
-        <v>49.5</v>
+        <v>47.3</v>
       </c>
       <c r="L5">
-        <v>49.3</v>
+        <v>46.7</v>
       </c>
       <c r="M5">
-        <v>48.8</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="N5">
-        <v>47.7</v>
+        <v>44</v>
       </c>
       <c r="O5">
-        <v>43.6</v>
+        <v>40.9</v>
       </c>
       <c r="P5">
-        <v>38.2</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -973,49 +973,49 @@
         <v>1</v>
       </c>
       <c r="B2">
+        <v>10.7</v>
+      </c>
+      <c r="C2">
+        <v>10.7</v>
+      </c>
+      <c r="D2">
+        <v>10.7</v>
+      </c>
+      <c r="E2">
+        <v>10.7</v>
+      </c>
+      <c r="F2">
         <v>10.6</v>
       </c>
-      <c r="C2">
+      <c r="G2">
         <v>10.6</v>
-      </c>
-      <c r="D2">
-        <v>10.6</v>
-      </c>
-      <c r="E2">
-        <v>10.8</v>
-      </c>
-      <c r="F2">
-        <v>10.7</v>
-      </c>
-      <c r="G2">
-        <v>10.5</v>
       </c>
       <c r="H2">
         <v>10.8</v>
       </c>
       <c r="I2">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="K2">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="L2">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
       <c r="M2">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="N2">
-        <v>18</v>
+        <v>20.9</v>
       </c>
       <c r="O2">
-        <v>28.3</v>
+        <v>32.2</v>
       </c>
       <c r="P2">
-        <v>30.4</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1023,49 +1023,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="C3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="D3">
-        <v>25.9</v>
+        <v>30.4</v>
       </c>
       <c r="E3">
-        <v>25.9</v>
+        <v>30.5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>30.6</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>30.7</v>
       </c>
       <c r="H3">
-        <v>26.5</v>
+        <v>31.1</v>
       </c>
       <c r="I3">
-        <v>26.7</v>
+        <v>31.5</v>
       </c>
       <c r="J3">
-        <v>27.3</v>
+        <v>31.8</v>
       </c>
       <c r="K3">
-        <v>29.1</v>
+        <v>34</v>
       </c>
       <c r="L3">
-        <v>30.7</v>
+        <v>35.8</v>
       </c>
       <c r="M3">
-        <v>31.9</v>
+        <v>37</v>
       </c>
       <c r="N3">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="O3">
-        <v>57.09999999999999</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="P3">
-        <v>74.40000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1073,49 +1073,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1123,49 +1123,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="F5">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="G5">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="H5">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="I5">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="J5">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="K5">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="L5">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="M5">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="N5">
-        <v>20.3</v>
+        <v>21.2</v>
       </c>
       <c r="O5">
-        <v>28.8</v>
+        <v>33.3</v>
       </c>
       <c r="P5">
-        <v>32.3</v>
+        <v>24.5</v>
       </c>
     </row>
   </sheetData>

--- a/temp/alpha_sweep_results.xlsx
+++ b/temp/alpha_sweep_results.xlsx
@@ -438,34 +438,34 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>26.5</v>
+        <v>25.6</v>
       </c>
       <c r="L2">
-        <v>30.3</v>
+        <v>27.8</v>
       </c>
       <c r="M2">
-        <v>32.5</v>
+        <v>29.9</v>
       </c>
       <c r="N2">
-        <v>41.5</v>
+        <v>38.9</v>
       </c>
       <c r="O2">
-        <v>67.5</v>
+        <v>55.60000000000001</v>
       </c>
       <c r="P2">
-        <v>99.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -473,49 +473,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>30.4</v>
+        <v>35.4</v>
       </c>
       <c r="C3">
-        <v>30.4</v>
+        <v>35.4</v>
       </c>
       <c r="D3">
-        <v>30.4</v>
+        <v>35.4</v>
       </c>
       <c r="E3">
-        <v>30.5</v>
+        <v>35.6</v>
       </c>
       <c r="F3">
-        <v>30.6</v>
+        <v>35.8</v>
       </c>
       <c r="G3">
-        <v>30.8</v>
+        <v>36.1</v>
       </c>
       <c r="H3">
-        <v>31.1</v>
+        <v>36.8</v>
       </c>
       <c r="I3">
-        <v>31.5</v>
+        <v>37.2</v>
       </c>
       <c r="J3">
-        <v>32.2</v>
+        <v>38.2</v>
       </c>
       <c r="K3">
-        <v>34.1</v>
+        <v>40</v>
       </c>
       <c r="L3">
-        <v>35.9</v>
+        <v>41.8</v>
       </c>
       <c r="M3">
-        <v>37.4</v>
+        <v>44.4</v>
       </c>
       <c r="N3">
-        <v>45.7</v>
+        <v>55.40000000000001</v>
       </c>
       <c r="O3">
-        <v>61.6</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>88.90000000000001</v>
+        <v>92.60000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -573,49 +573,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="E5">
-        <v>25.3</v>
+        <v>24.6</v>
       </c>
       <c r="F5">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
       <c r="G5">
-        <v>25.5</v>
+        <v>24.8</v>
       </c>
       <c r="H5">
+        <v>25.6</v>
+      </c>
+      <c r="I5">
+        <v>25.8</v>
+      </c>
+      <c r="J5">
         <v>26.1</v>
       </c>
-      <c r="I5">
-        <v>26.7</v>
-      </c>
-      <c r="J5">
-        <v>27.5</v>
-      </c>
       <c r="K5">
-        <v>29.2</v>
+        <v>28.5</v>
       </c>
       <c r="L5">
-        <v>32.1</v>
+        <v>30.2</v>
       </c>
       <c r="M5">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="N5">
-        <v>42.7</v>
+        <v>40.2</v>
       </c>
       <c r="O5">
-        <v>69.19999999999999</v>
+        <v>58.9</v>
       </c>
       <c r="P5">
-        <v>98.5</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -698,49 +698,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="C2">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="D2">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E2">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="F2">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="G2">
+        <v>52.1</v>
+      </c>
+      <c r="H2">
         <v>52</v>
       </c>
-      <c r="H2">
-        <v>51.8</v>
-      </c>
       <c r="I2">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="J2">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="K2">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="L2">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="M2">
-        <v>50.4</v>
+        <v>49.2</v>
       </c>
       <c r="N2">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="O2">
-        <v>43.5</v>
+        <v>38.9</v>
       </c>
       <c r="P2">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -748,49 +748,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="C3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="E3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="F3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="H3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="I3">
-        <v>96.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="J3">
-        <v>96.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K3">
-        <v>96.5</v>
+        <v>91.3</v>
       </c>
       <c r="L3">
-        <v>96.39999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="M3">
-        <v>96.2</v>
+        <v>91.10000000000001</v>
       </c>
       <c r="N3">
-        <v>95.5</v>
+        <v>90.7</v>
       </c>
       <c r="O3">
-        <v>94.3</v>
+        <v>89.8</v>
       </c>
       <c r="P3">
-        <v>90.40000000000001</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -851,46 +851,46 @@
         <v>48.5</v>
       </c>
       <c r="C5">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="D5">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E5">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="F5">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="G5">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="H5">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I5">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="J5">
         <v>47.9</v>
       </c>
       <c r="K5">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="L5">
-        <v>46.7</v>
+        <v>45.8</v>
       </c>
       <c r="M5">
-        <v>46.40000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="N5">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="O5">
-        <v>40.9</v>
+        <v>37.2</v>
       </c>
       <c r="P5">
-        <v>35</v>
+        <v>29.4</v>
       </c>
     </row>
   </sheetData>
@@ -973,49 +973,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="C2">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="D2">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="E2">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="F2">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="G2">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="H2">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="I2">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="J2">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="K2">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="L2">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
       <c r="M2">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="N2">
-        <v>20.9</v>
+        <v>18</v>
       </c>
       <c r="O2">
-        <v>32.2</v>
+        <v>25.3</v>
       </c>
       <c r="P2">
-        <v>24.8</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1023,49 +1023,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>30.4</v>
+        <v>34.8</v>
       </c>
       <c r="C3">
-        <v>30.4</v>
+        <v>34.8</v>
       </c>
       <c r="D3">
-        <v>30.4</v>
+        <v>34.8</v>
       </c>
       <c r="E3">
-        <v>30.5</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>30.6</v>
+        <v>35.2</v>
       </c>
       <c r="G3">
-        <v>30.7</v>
+        <v>35.4</v>
       </c>
       <c r="H3">
-        <v>31.1</v>
+        <v>36.2</v>
       </c>
       <c r="I3">
-        <v>31.5</v>
+        <v>36.5</v>
       </c>
       <c r="J3">
-        <v>31.8</v>
+        <v>37.4</v>
       </c>
       <c r="K3">
-        <v>34</v>
+        <v>39.1</v>
       </c>
       <c r="L3">
-        <v>35.8</v>
+        <v>40.5</v>
       </c>
       <c r="M3">
-        <v>37</v>
+        <v>42.8</v>
       </c>
       <c r="N3">
-        <v>44.4</v>
+        <v>50.7</v>
       </c>
       <c r="O3">
-        <v>54.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="P3">
-        <v>59.7</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1123,49 +1123,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="C5">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="D5">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="E5">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="F5">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="G5">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="H5">
+        <v>11.7</v>
+      </c>
+      <c r="I5">
+        <v>11.7</v>
+      </c>
+      <c r="J5">
         <v>12</v>
       </c>
-      <c r="I5">
-        <v>12.2</v>
-      </c>
-      <c r="J5">
-        <v>12.5</v>
-      </c>
       <c r="K5">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="L5">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="M5">
-        <v>16</v>
+        <v>14.3</v>
       </c>
       <c r="N5">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="O5">
-        <v>33.3</v>
+        <v>24.8</v>
       </c>
       <c r="P5">
-        <v>24.5</v>
+        <v>29.3</v>
       </c>
     </row>
   </sheetData>
